--- a/artfynd/A 31967-2023 artfynd.xlsx
+++ b/artfynd/A 31967-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31967-2023 artfynd.xlsx
+++ b/artfynd/A 31967-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81276874</v>
+        <v>81276877</v>
       </c>
       <c r="B2" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2668</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487022.0237768639</v>
+        <v>486990</v>
       </c>
       <c r="R2" t="n">
-        <v>6516109.153788167</v>
+        <v>6516109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hammar</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -748,19 +743,9 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>81276880</v>
       </c>
       <c r="B3" t="n">
-        <v>95220</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487025.1223188</v>
+        <v>487025</v>
       </c>
       <c r="R3" t="n">
-        <v>6516103.959547966</v>
+        <v>6516104</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-11-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +866,317 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>81276874</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aspabäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>487022</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6516109</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-11-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>81276878</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Aspabäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>487049</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6516081</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-11-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122660703</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Aspaån, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>487060</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6516082</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Elfiskestation</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Per Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31967-2023 artfynd.xlsx
+++ b/artfynd/A 31967-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81276877</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81276880</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81276874</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81276878</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122660703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>